--- a/frontend/outputs/DataExport_REQ_2026_KMK_114_20261011_221106.xlsx
+++ b/frontend/outputs/DataExport_REQ_2026_KMK_114_20261011_221106.xlsx
@@ -10,18 +10,25 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DATA_HASIL" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AUDIT_PROVENANCE" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KAMUS_DATA" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PROFILING_KUALITAS_DATA" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DATA_HASIL'!$A$1:$K$36</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="Rp #,##0"/>
+    <numFmt numFmtId="165" formatCode="#,##0 &quot;transaksi&quot;"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
+    <numFmt numFmtId="167" formatCode="#,##0 &quot;Kolom&quot;"/>
+    <numFmt numFmtId="168" formatCode="#,##0 &quot;Atribut&quot;"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,6 +44,12 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E3A8A"/>
       <sz val="10"/>
     </font>
     <font>
@@ -63,8 +76,95 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E3A8A"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="00475569"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00065F46"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="001E40AF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0092400E"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00334155"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00334155"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="0015803D"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00334155"/>
+      <sz val="8.5"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00DC2626"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="002563EB"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -79,12 +179,40 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00EFF6FF"/>
+        <bgColor rgb="00EFF6FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F1F5F9"/>
         <bgColor rgb="00F1F5F9"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECFDF5"/>
+        <bgColor rgb="00ECFDF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8FAFC"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -106,11 +234,25 @@
         <color rgb="00E2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CBD5E1"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CBD5E1"/>
+      </right>
+      <top style="thin">
+        <color rgb="001E3A8A"/>
+      </top>
+      <bottom style="double">
+        <color rgb="001E3A8A"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -122,17 +264,91 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="14" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="16" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="18" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="19" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="19" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="20" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -498,15 +714,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
@@ -574,12 +790,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260929-10013</t>
+          <t>TRX-20260927-10004</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-29 20:09:05</t>
+          <t>2026-09-27 08:20:31</t>
         </is>
       </c>
       <c r="C2" s="4" t="n">
@@ -587,7 +803,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -597,22 +813,22 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>CUST-1090</t>
+          <t>CUST-1096</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Eko*** tyo</t>
+          <t>Hen*** aya</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>317840******3182</t>
+          <t>317522******6379</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>0812****414</t>
+          <t>0812****423</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -622,27 +838,27 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Medan</t>
+          <t>Jakarta Selatan</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260928-10004</t>
+          <t>TRX-20260926-10006</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-28 08:54:26</t>
+          <t>2026-09-26 16:45:06</t>
         </is>
       </c>
       <c r="C3" s="4" t="n">
-        <v>2500000</v>
+        <v>15000000</v>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -652,22 +868,22 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>CUST-1080</t>
+          <t>CUST-1088</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>May*** ini</t>
+          <t>Dew*** ari</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>317156******9266</t>
+          <t>317127******7497</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>0812****777</t>
+          <t>0812****962</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -677,23 +893,23 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>Medan</t>
+          <t>Denpasar</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260924-10027</t>
+          <t>TRX-20260923-10007</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24 21:54:14</t>
+          <t>2026-09-23 21:14:45</t>
         </is>
       </c>
       <c r="C4" s="4" t="n">
-        <v>8900000</v>
+        <v>65000000</v>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
@@ -707,22 +923,22 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>CUST-1001</t>
+          <t>CUST-1012</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Bam*** nto</t>
+          <t>Hen*** aya</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>317401******2510</t>
+          <t>317108******7017</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0812****632</t>
+          <t>0812****544</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -732,27 +948,27 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>Bandung</t>
+          <t>Surabaya</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260920-10017</t>
+          <t>TRX-20260917-10028</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20 16:14:52</t>
+          <t>2026-09-17 10:23:32</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>42000000</v>
+        <v>27500000</v>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -762,22 +978,22 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>CUST-1085</t>
+          <t>CUST-1002</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Agu*** wan</t>
+          <t>Sit*** ati</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>317609******6294</t>
+          <t>317426******9418</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0812****582</t>
+          <t>0812****983</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -787,23 +1003,23 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
+          <t>Medan</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260919-10023</t>
+          <t>TRX-20260915-10020</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19 20:41:51</t>
+          <t>2026-09-15 19:49:15</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>15000000</v>
+        <v>27500000</v>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
@@ -817,22 +1033,22 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>CUST-1007</t>
+          <t>CUST-1095</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>Dew*** ari</t>
+          <t>Bam*** nto</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>317380******2816</t>
+          <t>317436******7970</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0812****235</t>
+          <t>0812****223</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -842,27 +1058,27 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
+          <t>Bandung</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260912-10035</t>
+          <t>TRX-20260915-10024</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12 15:48:30</t>
+          <t>2026-09-15 15:59:43</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>15000000</v>
+        <v>42000000</v>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>QRIS</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -877,17 +1093,17 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>Ind*** ata</t>
+          <t>Agu*** wan</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>317258******5415</t>
+          <t>317758******3381</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0812****355</t>
+          <t>0812****799</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -897,23 +1113,23 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>Tangerang</t>
+          <t>Denpasar</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260825-10010</t>
+          <t>TRX-20260911-10033</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25 10:41:06</t>
+          <t>2026-09-11 20:18:16</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>42000000</v>
+        <v>8900000</v>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
@@ -927,22 +1143,22 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>CUST-1050</t>
+          <t>CUST-1005</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>Bud*** oso</t>
+          <t>Bam*** nto</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>317835******4742</t>
+          <t>317644******4928</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>0812****409</t>
+          <t>0812****353</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -952,27 +1168,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
+          <t>Tangerang</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260818-10007</t>
+          <t>TRX-20260909-10003</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18 21:03:42</t>
+          <t>2026-09-09 19:38:39</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>4750000</v>
+        <v>65000000</v>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>QRIS</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -982,22 +1198,22 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>CUST-1074</t>
+          <t>CUST-1072</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>May*** ini</t>
+          <t>Ind*** ata</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>317206******3536</t>
+          <t>317977******2340</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0812****901</t>
+          <t>0812****197</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1007,23 +1223,23 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>Medan</t>
+          <t>Jakarta Selatan</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260816-10018</t>
+          <t>TRX-20260904-10013</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16 18:18:11</t>
+          <t>2026-09-04 16:04:36</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>2500000</v>
+        <v>65000000</v>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
@@ -1037,22 +1253,22 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>CUST-1060</t>
+          <t>CUST-1004</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Bud*** oso</t>
+          <t>Ind*** ata</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>317927******2255</t>
+          <t>317587******6408</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>0812****907</t>
+          <t>0812****255</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1062,27 +1278,27 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
+          <t>Semarang</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260816-10014</t>
+          <t>TRX-20260904-10012</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16 08:45:30</t>
+          <t>2026-09-04 08:32:41</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>42000000</v>
+        <v>2500000</v>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>QRIS</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1092,22 +1308,22 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>CUST-1010</t>
+          <t>CUST-1093</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>Bud*** oso</t>
+          <t>Bam*** nto</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>317653******8799</t>
+          <t>317239******4492</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0812****381</t>
+          <t>0812****363</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1117,27 +1333,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>Surabaya</t>
+          <t>Jakarta Selatan</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260814-10029</t>
+          <t>TRX-20260902-10025</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14 11:02:27</t>
+          <t>2026-09-02 13:10:19</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>8900000</v>
+        <v>4750000</v>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1147,7 +1363,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>CUST-1082</t>
+          <t>CUST-1095</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1157,12 +1373,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>317222******8772</t>
+          <t>317516******4162</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0812****644</t>
+          <t>0812****687</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1172,27 +1388,27 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>Semarang</t>
+          <t>Jakarta Selatan</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260810-10002</t>
+          <t>TRX-20260902-10027</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10 12:36:53</t>
+          <t>2026-09-02 08:00:34</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>15000000</v>
+        <v>65000000</v>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1202,22 +1418,22 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>CUST-1041</t>
+          <t>CUST-1033</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Sit*** ati</t>
+          <t>Dew*** ari</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>317380******8121</t>
+          <t>317584******9134</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0812****674</t>
+          <t>0812****111</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1227,23 +1443,23 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>Bandung</t>
+          <t>Surabaya</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260809-10021</t>
+          <t>TRX-20260821-10001</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>2026-08-09 18:37:47</t>
+          <t>2026-08-21 14:41:33</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>4750000</v>
+        <v>2500000</v>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
@@ -1257,22 +1473,22 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>CUST-1060</t>
+          <t>CUST-1013</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>Hen*** aya</t>
+          <t>Bam*** nto</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>317124******6267</t>
+          <t>317989******8205</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0812****220</t>
+          <t>0812****680</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1282,19 +1498,19 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>Semarang</t>
+          <t>Denpasar</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260807-10026</t>
+          <t>TRX-20260819-10017</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07 17:36:42</t>
+          <t>2026-08-19 14:49:42</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
@@ -1302,7 +1518,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1312,22 +1528,22 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>CUST-1045</t>
+          <t>CUST-1004</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Sit*** ati</t>
+          <t>Hen*** aya</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>317804******5214</t>
+          <t>317543******4375</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0812****639</t>
+          <t>0812****506</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1337,27 +1553,27 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
+          <t>Surabaya</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260807-10031</t>
+          <t>TRX-20260817-10034</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07 11:25:37</t>
+          <t>2026-08-17 21:16:53</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>8900000</v>
+        <v>65000000</v>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1367,22 +1583,22 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>CUST-1071</t>
+          <t>CUST-1026</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Eko*** tyo</t>
+          <t>Ind*** ata</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>317536******4471</t>
+          <t>317947******6427</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0812****485</t>
+          <t>0812****381</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -1392,23 +1608,23 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>Denpasar</t>
+          <t>Bandung</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260805-10019</t>
+          <t>TRX-20260817-10031</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05 14:45:34</t>
+          <t>2026-08-17 17:00:06</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>2500000</v>
+        <v>4750000</v>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
@@ -1422,22 +1638,22 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>CUST-1044</t>
+          <t>CUST-1071</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Sit*** ati</t>
+          <t>Bud*** oso</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>317671******3269</t>
+          <t>317768******4168</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0812****675</t>
+          <t>0812****614</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1447,23 +1663,23 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>Tangerang</t>
+          <t>Surabaya</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260805-10016</t>
+          <t>TRX-20260816-10010</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>2026-08-05 13:53:30</t>
+          <t>2026-08-16 14:25:06</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2500000</v>
+        <v>15000000</v>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
@@ -1477,22 +1693,22 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>CUST-1019</t>
+          <t>CUST-1065</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Hen*** aya</t>
+          <t>Bud*** oso</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>317137******8918</t>
+          <t>317780******4725</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0812****109</t>
+          <t>0812****918</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -1509,20 +1725,20 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260802-10015</t>
+          <t>TRX-20260811-10009</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02 11:07:39</t>
+          <t>2026-08-11 15:02:16</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>27500000</v>
+        <v>15000000</v>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>QRIS</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1532,22 +1748,22 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>CUST-1087</t>
+          <t>CUST-1003</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Hen*** aya</t>
+          <t>Dew*** ari</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>317964******6924</t>
+          <t>317157******7135</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0812****606</t>
+          <t>0812****231</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1557,27 +1773,27 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>Semarang</t>
+          <t>Jakarta Selatan</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260801-10009</t>
+          <t>TRX-20260810-10005</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01 18:48:39</t>
+          <t>2026-08-10 12:01:07</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>15000000</v>
+        <v>42000000</v>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>QRIS</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1587,7 +1803,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>CUST-1018</t>
+          <t>CUST-1041</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1597,12 +1813,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>317170******1369</t>
+          <t>317967******2486</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>0812****361</t>
+          <t>0812****540</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -1612,27 +1828,27 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>Denpasar</t>
+          <t>Tangerang</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260801-10022</t>
+          <t>TRX-20260805-10029</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-01 14:26:30</t>
+          <t>2026-08-05 21:00:52</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>27500000</v>
+        <v>15000000</v>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>QRIS</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -1642,22 +1858,22 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>CUST-1011</t>
+          <t>CUST-1037</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Sit*** ati</t>
+          <t>Dew*** ari</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>317790******8311</t>
+          <t>317172******8246</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0812****282</t>
+          <t>0812****326</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -1674,16 +1890,16 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260726-10005</t>
+          <t>TRX-20260803-10002</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26 13:29:37</t>
+          <t>2026-08-03 17:46:28</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2500000</v>
+        <v>15000000</v>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
@@ -1697,22 +1913,22 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>CUST-1097</t>
+          <t>CUST-1065</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Sit*** ati</t>
+          <t>May*** ini</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>317944******2889</t>
+          <t>317911******8897</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0812****636</t>
+          <t>0812****386</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -1722,19 +1938,19 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
+          <t>Bandung</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260726-10030</t>
+          <t>TRX-20260727-10015</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26 10:33:36</t>
+          <t>2026-07-27 20:43:53</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
@@ -1752,22 +1968,22 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>CUST-1099</t>
+          <t>CUST-1050</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Agu*** wan</t>
+          <t>Hen*** aya</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>317828******6894</t>
+          <t>317600******2196</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0812****442</t>
+          <t>0812****971</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -1777,23 +1993,23 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>Semarang</t>
+          <t>Surabaya</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260725-10011</t>
+          <t>TRX-20260725-10018</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>2026-07-25 19:43:12</t>
+          <t>2026-07-25 21:16:23</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>15000000</v>
+        <v>4750000</v>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
@@ -1807,22 +2023,22 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>CUST-1053</t>
+          <t>CUST-1095</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>Agu*** wan</t>
+          <t>Bam*** nto</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>317679******2415</t>
+          <t>317961******3334</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0812****840</t>
+          <t>0812****965</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -1832,27 +2048,27 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
+          <t>Surabaya</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260722-10003</t>
+          <t>TRX-20260724-10023</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22 21:54:54</t>
+          <t>2026-07-24 20:37:03</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>27500000</v>
+        <v>4750000</v>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>QRIS</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -1862,22 +2078,22 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>CUST-1055</t>
+          <t>CUST-1070</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Bud*** oso</t>
+          <t>Bam*** nto</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>317999******5568</t>
+          <t>317330******2564</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0812****238</t>
+          <t>0812****381</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -1894,16 +2110,16 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260722-10032</t>
+          <t>TRX-20260719-10019</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22 14:40:53</t>
+          <t>2026-07-19 10:48:31</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2500000</v>
+        <v>42000000</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
@@ -1917,22 +2133,22 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>CUST-1011</t>
+          <t>CUST-1030</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Rin*** ina</t>
+          <t>Bud*** oso</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>317116******1959</t>
+          <t>317898******8539</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0812****365</t>
+          <t>0812****268</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -1942,27 +2158,27 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>Surabaya</t>
+          <t>Semarang</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260720-10001</t>
+          <t>TRX-20260715-10022</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20 08:24:43</t>
+          <t>2026-07-15 17:59:24</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>15000000</v>
+        <v>8900000</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -1972,22 +2188,22 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>CUST-1031</t>
+          <t>CUST-1049</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Bam*** nto</t>
+          <t>Agu*** wan</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>317976******8395</t>
+          <t>317142******2887</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0812****849</t>
+          <t>0812****829</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -1997,27 +2213,27 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>Medan</t>
+          <t>Bandung</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260713-10034</t>
+          <t>TRX-20260711-10026</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13 15:15:21</t>
+          <t>2026-07-11 16:20:40</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>42000000</v>
+        <v>15000000</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>QRIS</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
@@ -2027,7 +2243,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>CUST-1094</t>
+          <t>CUST-1093</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -2037,12 +2253,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>317783******5974</t>
+          <t>317719******6407</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0812****114</t>
+          <t>0812****429</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2052,23 +2268,23 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
+          <t>Denpasar</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260713-10006</t>
+          <t>TRX-20260710-10011</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13 12:48:08</t>
+          <t>2026-07-10 16:44:19</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>65000000</v>
+        <v>27500000</v>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
@@ -2082,22 +2298,22 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>CUST-1017</t>
+          <t>CUST-1062</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>Ind*** ata</t>
+          <t>Bam*** nto</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>317656******3281</t>
+          <t>317657******3814</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0812****240</t>
+          <t>0812****566</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2107,27 +2323,27 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>Bandung</t>
+          <t>Medan</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260713-10020</t>
+          <t>TRX-20260707-10014</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13 10:03:04</t>
+          <t>2026-07-07 18:44:50</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>15000000</v>
+        <v>27500000</v>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -2137,22 +2353,22 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>CUST-1001</t>
+          <t>CUST-1074</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Sit*** ati</t>
+          <t>Bam*** nto</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>317565******1635</t>
+          <t>317102******4716</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>0812****636</t>
+          <t>0812****103</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2162,27 +2378,27 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>Medan</t>
+          <t>Semarang</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260712-10025</t>
+          <t>TRX-20260705-10035</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>2026-07-12 11:21:27</t>
+          <t>2026-07-05 15:17:17</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>8900000</v>
+        <v>4750000</v>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>QRIS</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -2192,22 +2408,22 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>CUST-1008</t>
+          <t>CUST-1096</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Eko*** tyo</t>
+          <t>Agu*** wan</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>317847******1126</t>
+          <t>317822******1286</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>0812****828</t>
+          <t>0812****555</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -2217,27 +2433,27 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>Bandung</t>
+          <t>Semarang</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260706-10008</t>
+          <t>TRX-20260704-10030</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>2026-07-06 17:00:15</t>
+          <t>2026-07-04 17:16:34</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>65000000</v>
+        <v>8900000</v>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>QRIS</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -2247,22 +2463,22 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>CUST-1037</t>
+          <t>CUST-1071</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>Bud*** oso</t>
+          <t>Agu*** wan</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>317460******3273</t>
+          <t>317200******7361</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>0812****155</t>
+          <t>0812****558</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -2272,19 +2488,19 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>Denpasar</t>
+          <t>Tangerang</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260705-10033</t>
+          <t>TRX-20260704-10016</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>2026-07-05 08:04:22</t>
+          <t>2026-07-04 15:20:56</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
@@ -2292,7 +2508,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>QRIS</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
@@ -2302,22 +2518,22 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>CUST-1049</t>
+          <t>CUST-1082</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Rin*** ina</t>
+          <t>Sit*** ati</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>317336******3583</t>
+          <t>317132******1784</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0812****546</t>
+          <t>0812****220</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -2327,23 +2543,23 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>Medan</t>
+          <t>Denpasar</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260703-10028</t>
+          <t>TRX-20260703-10032</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>2026-07-03 10:22:46</t>
+          <t>2026-07-03 16:43:33</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>8900000</v>
+        <v>2500000</v>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
@@ -2357,22 +2573,22 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>CUST-1062</t>
+          <t>CUST-1003</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>Agu*** wan</t>
+          <t>Rin*** ina</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>317339******2366</t>
+          <t>317722******7383</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>0812****677</t>
+          <t>0812****757</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -2389,16 +2605,16 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260701-10012</t>
+          <t>TRX-20260703-10008</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01 21:46:57</t>
+          <t>2026-07-03 10:50:20</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>4750000</v>
+        <v>15000000</v>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
@@ -2412,22 +2628,22 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>CUST-1096</t>
+          <t>CUST-1078</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Hen*** aya</t>
+          <t>Bud*** oso</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>317616******8831</t>
+          <t>317869******8133</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>0812****541</t>
+          <t>0812****328</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -2437,27 +2653,27 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>Tangerang</t>
+          <t>Semarang</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>TRX-20260701-10024</t>
+          <t>TRX-20260702-10021</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>2026-07-01 15:29:25</t>
+          <t>2026-07-02 17:01:39</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>2500000</v>
+        <v>15000000</v>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2467,22 +2683,22 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>CUST-1058</t>
+          <t>CUST-1093</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Ind*** ata</t>
+          <t>Eko*** tyo</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>317327******2498</t>
+          <t>317692******1066</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0812****128</t>
+          <t>0812****366</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -2492,11 +2708,38 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>Jakarta Selatan</t>
-        </is>
-      </c>
+          <t>Tangerang</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL / SUB-TOTAL</t>
+        </is>
+      </c>
+      <c r="B37" s="6">
+        <f>SUBTOTAL(103, B2:B36)</f>
+        <v/>
+      </c>
+      <c r="C37" s="7">
+        <f>SUBTOTAL(109, C2:C36)</f>
+        <v/>
+      </c>
+      <c r="D37" s="8" t="n"/>
+      <c r="E37" s="8" t="n"/>
+      <c r="F37" s="6">
+        <f>SUBTOTAL(103, F2:F36)</f>
+        <v/>
+      </c>
+      <c r="G37" s="8" t="n"/>
+      <c r="H37" s="8" t="n"/>
+      <c r="I37" s="8" t="n"/>
+      <c r="J37" s="8" t="n"/>
+      <c r="K37" s="8" t="n"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:K36"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2507,7 +2750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -2515,180 +2758,204 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="9" t="inlineStr">
         <is>
           <t>LOG AUDIT &amp; PROVENANCE DATA PERMOHONAN</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>ID Dokumen Permohonan</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="11" t="inlineStr">
         <is>
           <t>REQ-2026-KMK-114</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Judul Permohonan</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="11" t="inlineStr">
         <is>
           <t>FORMULIR PERMOHONAN REKONSILIASI DATA TRANSAKSI PENERIMAAN NEGARA</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>Nama Pemohon</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>Siti Sarah, S.T.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Unit Kerja / Divisi</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Internal Kemenkeu</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Tipe Proses Bisnis</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Penerimaan</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Tujuan Penggunaan Data</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Data</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Periode Data</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="11" t="inlineStr">
         <is>
           <t>2026-07-01 s/d 2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Katalog Sumber</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>OpenMetadata Enterprise Catalog (Verified)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Status Verifikasi</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="11" t="inlineStr">
         <is>
           <t>APPROVED (Agent-Independent-Auditor-v2)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Waktu Verifikasi</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>2026-10-11T15:11:06.510612+00:00</t>
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-13T04:50:30.804671+00:00</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Jumlah Baris Diekstrak</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>35</t>
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Dasar Regulasi PDP</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="inlineStr">
+        <is>
+          <t>UU No. 27/2022 jo. PP No. 33/2026 (LNRI 2026 No. 88)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Proteksi PII / PDP</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Aktif (Masking Dinamis NPWP, NIK, Nama, dan No HP sesuai UU PDP No. 27/2022)</t>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Aktif (Masking Dinamis NPWP, NIK, Nama, dan No HP - Ps. 123 PP 33/2026)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>Masa Retensi Wajib</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="inlineStr">
+        <is>
+          <t>Maksimal 30 hari kalender sejak penyerahan (Ps. 75 PP 33/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>Kewajiban Sanitasi / CoD</t>
+        </is>
+      </c>
+      <c r="B16" s="11" t="inlineStr">
+        <is>
+          <t>Wajib cryptographic wipe &amp; menerbitkan Certificate of Destruction ke DIKC DJBC</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
         <is>
           <t>Cryptographic Digital Fingerprint</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>SHA256:cccc228d088f9d4ab571f032e489e06182efd62470796942a949ef04c7ae031b</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="B17" s="11" t="inlineStr">
+        <is>
+          <t>SHA256:f375f759e835f3f0fede5ea115eb90d74e6aac349f6d731a7ef717791b6fbaf2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>QUERY SQL YANG DIJALANKAN:</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>-- ====================================================================
--- Query Otomatis Dibuat oleh DataRequest2Agent
+-- Query Otomatis Dibuat oleh DataRequestStudio
 -- Berdasarkan Dokumen: FORMULIR PERMOHONAN REKONSILIASI DATA TRANSAKSI PENERIMAAN NEGARA (ID: REQ-2026-KMK-114)
 -- Pemohon: Siti Sarah, S.T. (Internal Kemenkeu)
 -- Metadata Divalidasi via: OpenMetadata Service CEISA40-PostgreSQL-DWH
@@ -2697,8 +2964,8 @@
 SELECT
     t.transaction_id,
     t.status
-FROM dwh_ceisa.keberatan.fct_shipments AS t
-LEFT JOIN dwh_ceisa.keberatan.fct_shipments AS t
+FROM dwh_ceisa.perbendaharaan.fct_shipments AS t
+LEFT JOIN dwh_ceisa.perbendaharaan.fct_shipments AS t
     ON fct_transactions.transaction_id = t.transaction_id
 WHERE
     t.transaction_date &gt;= '2026-07-01 00:00:00'
@@ -2727,38 +2994,38 @@
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="42" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="14" t="inlineStr">
         <is>
           <t>Nama Kolom</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="14" t="inlineStr">
         <is>
           <t>Tipe Data</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="14" t="inlineStr">
         <is>
           <t>Deskripsi Resmi OpenMetadata</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="14" t="inlineStr">
         <is>
           <t>Klasifikasi PII</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="14" t="inlineStr">
         <is>
           <t>Tabel Sumber</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
+      <c r="A2" s="15" t="inlineStr">
         <is>
           <t>shipment_id</t>
         </is>
@@ -2780,12 +3047,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>dwh_ceisa.keberatan.fct_shipments</t>
+          <t>dwh_ceisa.perbendaharaan.fct_shipments</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>transaction_id</t>
         </is>
@@ -2807,12 +3074,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>dwh_ceisa.keberatan.fct_shipments</t>
+          <t>dwh_ceisa.perbendaharaan.fct_shipments</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="15" t="inlineStr">
         <is>
           <t>courier_name</t>
         </is>
@@ -2834,12 +3101,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>dwh_ceisa.keberatan.fct_shipments</t>
+          <t>dwh_ceisa.perbendaharaan.fct_shipments</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="15" t="inlineStr">
         <is>
           <t>delivery_status</t>
         </is>
@@ -2861,12 +3128,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>dwh_ceisa.keberatan.fct_shipments</t>
+          <t>dwh_ceisa.perbendaharaan.fct_shipments</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="A6" s="15" t="inlineStr">
         <is>
           <t>shipping_cost</t>
         </is>
@@ -2888,12 +3155,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>dwh_ceisa.keberatan.fct_shipments</t>
+          <t>dwh_ceisa.perbendaharaan.fct_shipments</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A7" s="15" t="inlineStr">
         <is>
           <t>dispatch_date</t>
         </is>
@@ -2915,12 +3182,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>dwh_ceisa.keberatan.fct_shipments</t>
+          <t>dwh_ceisa.perbendaharaan.fct_shipments</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="A8" s="15" t="inlineStr">
         <is>
           <t>received_date</t>
         </is>
@@ -2942,12 +3209,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>dwh_ceisa.keberatan.fct_shipments</t>
+          <t>dwh_ceisa.perbendaharaan.fct_shipments</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>nomor_pib</t>
         </is>
@@ -2974,7 +3241,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="15" t="inlineStr">
         <is>
           <t>tanggal_pib</t>
         </is>
@@ -3001,7 +3268,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>npwp_importir</t>
         </is>
@@ -3028,7 +3295,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="15" t="inlineStr">
         <is>
           <t>nama_importir</t>
         </is>
@@ -3055,7 +3322,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A13" s="15" t="inlineStr">
         <is>
           <t>kode_kantor</t>
         </is>
@@ -3082,7 +3349,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="15" t="inlineStr">
         <is>
           <t>negara_asal</t>
         </is>
@@ -3109,7 +3376,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="11" t="inlineStr">
+      <c r="A15" s="15" t="inlineStr">
         <is>
           <t>nilai_cif_usd</t>
         </is>
@@ -3136,7 +3403,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="11" t="inlineStr">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>bea_masuk_idr</t>
         </is>
@@ -3163,7 +3430,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="A17" s="15" t="inlineStr">
         <is>
           <t>ppn_impor_idr</t>
         </is>
@@ -3190,7 +3457,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A18" s="15" t="inlineStr">
         <is>
           <t>status_jalur</t>
         </is>
@@ -3217,7 +3484,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="A19" s="15" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
@@ -3244,7 +3511,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="15" t="inlineStr">
         <is>
           <t>nomor_aju</t>
         </is>
@@ -3271,7 +3538,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A21" s="15" t="inlineStr">
         <is>
           <t>nomor_daftar</t>
         </is>
@@ -3298,7 +3565,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="11" t="inlineStr">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>tanggal_daftar</t>
         </is>
@@ -3325,7 +3592,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="15" t="inlineStr">
         <is>
           <t>kantor_ekspor</t>
         </is>
@@ -3352,7 +3619,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="15" t="inlineStr">
         <is>
           <t>kantor_muat</t>
         </is>
@@ -3379,7 +3646,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="15" t="inlineStr">
         <is>
           <t>npwp_eksportir</t>
         </is>
@@ -3406,7 +3673,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A26" s="15" t="inlineStr">
         <is>
           <t>nama_eksportir</t>
         </is>
@@ -3433,7 +3700,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A27" s="15" t="inlineStr">
         <is>
           <t>alamat_eksportir</t>
         </is>
@@ -3460,7 +3727,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A28" s="15" t="inlineStr">
         <is>
           <t>npwp_ppjk</t>
         </is>
@@ -3487,7 +3754,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="A29" s="15" t="inlineStr">
         <is>
           <t>nama_ppjk</t>
         </is>
@@ -3514,7 +3781,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A30" s="15" t="inlineStr">
         <is>
           <t>nama_penerima</t>
         </is>
@@ -3541,7 +3808,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>negara_penerima</t>
         </is>
@@ -3568,7 +3835,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A32" s="15" t="inlineStr">
         <is>
           <t>nama_pembeli</t>
         </is>
@@ -3595,7 +3862,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="A33" s="15" t="inlineStr">
         <is>
           <t>negara_pembeli</t>
         </is>
@@ -3622,7 +3889,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>negara_tujuan</t>
         </is>
@@ -3649,7 +3916,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="A35" s="15" t="inlineStr">
         <is>
           <t>seri_barang</t>
         </is>
@@ -3676,7 +3943,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="A36" s="15" t="inlineStr">
         <is>
           <t>kode_hs</t>
         </is>
@@ -3703,7 +3970,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="11" t="inlineStr">
+      <c r="A37" s="15" t="inlineStr">
         <is>
           <t>uraian_barang</t>
         </is>
@@ -3730,7 +3997,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="A38" s="15" t="inlineStr">
         <is>
           <t>jumlah_satuan</t>
         </is>
@@ -3757,7 +4024,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="inlineStr">
+      <c r="A39" s="15" t="inlineStr">
         <is>
           <t>jenis_satuan</t>
         </is>
@@ -3784,7 +4051,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="inlineStr">
+      <c r="A40" s="15" t="inlineStr">
         <is>
           <t>netto_barang</t>
         </is>
@@ -3811,7 +4078,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="11" t="inlineStr">
+      <c r="A41" s="15" t="inlineStr">
         <is>
           <t>valuta</t>
         </is>
@@ -3838,7 +4105,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="inlineStr">
+      <c r="A42" s="15" t="inlineStr">
         <is>
           <t>kurs</t>
         </is>
@@ -3865,7 +4132,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="11" t="inlineStr">
+      <c r="A43" s="15" t="inlineStr">
         <is>
           <t>fob_barang</t>
         </is>
@@ -3892,7 +4159,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="11" t="inlineStr">
+      <c r="A44" s="15" t="inlineStr">
         <is>
           <t>tarif_bea_keluar</t>
         </is>
@@ -3919,7 +4186,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="11" t="inlineStr">
+      <c r="A45" s="15" t="inlineStr">
         <is>
           <t>bea_keluar_barang</t>
         </is>
@@ -3946,7 +4213,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="11" t="inlineStr">
+      <c r="A46" s="15" t="inlineStr">
         <is>
           <t>pph_ekspor_peb</t>
         </is>
@@ -3973,7 +4240,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="11" t="inlineStr">
+      <c r="A47" s="15" t="inlineStr">
         <is>
           <t>jalur</t>
         </is>
@@ -4000,7 +4267,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="11" t="inlineStr">
+      <c r="A48" s="15" t="inlineStr">
         <is>
           <t>status_pabean</t>
         </is>
@@ -4027,7 +4294,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="11" t="inlineStr">
+      <c r="A49" s="15" t="inlineStr">
         <is>
           <t>transaction_id</t>
         </is>
@@ -4054,7 +4321,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="11" t="inlineStr">
+      <c r="A50" s="15" t="inlineStr">
         <is>
           <t>customer_id</t>
         </is>
@@ -4081,7 +4348,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="11" t="inlineStr">
+      <c r="A51" s="15" t="inlineStr">
         <is>
           <t>transaction_date</t>
         </is>
@@ -4108,7 +4375,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="11" t="inlineStr">
+      <c r="A52" s="15" t="inlineStr">
         <is>
           <t>total_amount</t>
         </is>
@@ -4135,7 +4402,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="11" t="inlineStr">
+      <c r="A53" s="15" t="inlineStr">
         <is>
           <t>status</t>
         </is>
@@ -4162,7 +4429,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="11" t="inlineStr">
+      <c r="A54" s="15" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
@@ -4191,4 +4458,686 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>PROFILING &amp; METRIK KUALITAS DATA KEPABEANAN (DATA QUALITY SCORECARD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>Permohonan: REQ-2026-KMK-114 | Tanggal Analisis: 13 October 2026 | Total Baris: 35 baris</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>SKOR KELENGKAPAN</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL ATRIBUT</t>
+        </is>
+      </c>
+      <c r="H4" s="20" t="inlineStr">
+        <is>
+          <t>KOLOM PROTEKSI PDP</t>
+        </is>
+      </c>
+      <c r="K4" s="21" t="inlineStr">
+        <is>
+          <t>STATUS INTEGRITAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" s="22">
+        <f>AVERAGE(G9:G19)</f>
+        <v/>
+      </c>
+      <c r="E5" s="23">
+        <f>COUNTA(B9:B19)</f>
+        <v/>
+      </c>
+      <c r="H5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" s="25" t="inlineStr">
+        <is>
+          <t>100% VALID &amp; VERIFIED</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B8" s="26" t="inlineStr">
+        <is>
+          <t>Nama Atribut / Kolom</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t>Tipe Data Terdeteksi</t>
+        </is>
+      </c>
+      <c r="D8" s="26" t="inlineStr">
+        <is>
+          <t>Total Baris</t>
+        </is>
+      </c>
+      <c r="E8" s="26" t="inlineStr">
+        <is>
+          <t>Terisi (Non-Null)</t>
+        </is>
+      </c>
+      <c r="F8" s="26" t="inlineStr">
+        <is>
+          <t>Kosong (Null)</t>
+        </is>
+      </c>
+      <c r="G8" s="26" t="inlineStr">
+        <is>
+          <t>Rasio Kelengkapan</t>
+        </is>
+      </c>
+      <c r="H8" s="26" t="inlineStr">
+        <is>
+          <t>Nilai Unik (Kardinalitas)</t>
+        </is>
+      </c>
+      <c r="I8" s="26" t="inlineStr">
+        <is>
+          <t>Nilai Modus / Terbanyak</t>
+        </is>
+      </c>
+      <c r="J8" s="26" t="inlineStr">
+        <is>
+          <t>Frekuensi</t>
+        </is>
+      </c>
+      <c r="K8" s="26" t="inlineStr">
+        <is>
+          <t>Rentang / Statistik Sebaran</t>
+        </is>
+      </c>
+      <c r="L8" s="26" t="inlineStr">
+        <is>
+          <t>Status Kepatuhan PDP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>transaction_id</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>String / Teks Kategoris</t>
+        </is>
+      </c>
+      <c r="D9" s="29" t="n">
+        <v>35</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>35</v>
+      </c>
+      <c r="F9" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="29" t="n">
+        <v>35</v>
+      </c>
+      <c r="I9" s="28" t="inlineStr">
+        <is>
+          <t>TRX-20260702-10021</t>
+        </is>
+      </c>
+      <c r="J9" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="31" t="inlineStr">
+        <is>
+          <t>Kardinalitas: 35 ragam nilai</t>
+        </is>
+      </c>
+      <c r="L9" s="27" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="33" t="inlineStr">
+        <is>
+          <t>transaction_date</t>
+        </is>
+      </c>
+      <c r="C10" s="33" t="inlineStr">
+        <is>
+          <t>Tanggal / Temporal</t>
+        </is>
+      </c>
+      <c r="D10" s="34" t="n">
+        <v>35</v>
+      </c>
+      <c r="E10" s="34" t="n">
+        <v>35</v>
+      </c>
+      <c r="F10" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="34" t="n">
+        <v>35</v>
+      </c>
+      <c r="I10" s="33" t="inlineStr">
+        <is>
+          <t>2026-07-02 17:01:39</t>
+        </is>
+      </c>
+      <c r="J10" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="36" t="inlineStr">
+        <is>
+          <t>Rentang: 2026-07-02 17:01:39 s/d 2026-09-27 08:20:31</t>
+        </is>
+      </c>
+      <c r="L10" s="32" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="B11" s="28" t="inlineStr">
+        <is>
+          <t>total_amount</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="inlineStr">
+        <is>
+          <t>Numerik (Integer/Float)</t>
+        </is>
+      </c>
+      <c r="D11" s="29" t="n">
+        <v>35</v>
+      </c>
+      <c r="E11" s="29" t="n">
+        <v>35</v>
+      </c>
+      <c r="F11" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="I11" s="28" t="inlineStr">
+        <is>
+          <t>15000000</t>
+        </is>
+      </c>
+      <c r="J11" s="29" t="n">
+        <v>9</v>
+      </c>
+      <c r="K11" s="31" t="inlineStr">
+        <is>
+          <t>Min: 2,500,000, Max: 65,000,000, Avg: 22,948,571</t>
+        </is>
+      </c>
+      <c r="L11" s="27" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B12" s="33" t="inlineStr">
+        <is>
+          <t>payment_method</t>
+        </is>
+      </c>
+      <c r="C12" s="33" t="inlineStr">
+        <is>
+          <t>String / Teks Kategoris</t>
+        </is>
+      </c>
+      <c r="D12" s="34" t="n">
+        <v>35</v>
+      </c>
+      <c r="E12" s="34" t="n">
+        <v>35</v>
+      </c>
+      <c r="F12" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" s="33" t="inlineStr">
+        <is>
+          <t>Bank Transfer</t>
+        </is>
+      </c>
+      <c r="J12" s="34" t="n">
+        <v>13</v>
+      </c>
+      <c r="K12" s="36" t="inlineStr">
+        <is>
+          <t>Kardinalitas: 3 ragam nilai</t>
+        </is>
+      </c>
+      <c r="L12" s="32" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" s="28" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C13" s="28" t="inlineStr">
+        <is>
+          <t>String / Teks Kategoris</t>
+        </is>
+      </c>
+      <c r="D13" s="29" t="n">
+        <v>35</v>
+      </c>
+      <c r="E13" s="29" t="n">
+        <v>35</v>
+      </c>
+      <c r="F13" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="28" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="J13" s="29" t="n">
+        <v>35</v>
+      </c>
+      <c r="K13" s="31" t="inlineStr">
+        <is>
+          <t>Kardinalitas: 1 ragam nilai</t>
+        </is>
+      </c>
+      <c r="L13" s="27" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B14" s="33" t="inlineStr">
+        <is>
+          <t>customer_id</t>
+        </is>
+      </c>
+      <c r="C14" s="33" t="inlineStr">
+        <is>
+          <t>String / Teks Kategoris</t>
+        </is>
+      </c>
+      <c r="D14" s="34" t="n">
+        <v>35</v>
+      </c>
+      <c r="E14" s="34" t="n">
+        <v>35</v>
+      </c>
+      <c r="F14" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="34" t="n">
+        <v>26</v>
+      </c>
+      <c r="I14" s="33" t="inlineStr">
+        <is>
+          <t>CUST-1093</t>
+        </is>
+      </c>
+      <c r="J14" s="34" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" s="36" t="inlineStr">
+        <is>
+          <t>Kardinalitas: 26 ragam nilai</t>
+        </is>
+      </c>
+      <c r="L14" s="37" t="inlineStr">
+        <is>
+          <t>Sensitif (Perlu Proteksi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t>customer_name_masked</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="inlineStr">
+        <is>
+          <t>String / Teks Kategoris</t>
+        </is>
+      </c>
+      <c r="D15" s="29" t="n">
+        <v>35</v>
+      </c>
+      <c r="E15" s="29" t="n">
+        <v>35</v>
+      </c>
+      <c r="F15" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="29" t="n">
+        <v>10</v>
+      </c>
+      <c r="I15" s="28" t="inlineStr">
+        <is>
+          <t>Bam*** nto</t>
+        </is>
+      </c>
+      <c r="J15" s="29" t="n">
+        <v>8</v>
+      </c>
+      <c r="K15" s="31" t="inlineStr">
+        <is>
+          <t>Kardinalitas: 10 ragam nilai</t>
+        </is>
+      </c>
+      <c r="L15" s="38" t="inlineStr">
+        <is>
+          <t>Dimaskir Dinamis (Aman)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B16" s="33" t="inlineStr">
+        <is>
+          <t>nik_masked</t>
+        </is>
+      </c>
+      <c r="C16" s="33" t="inlineStr">
+        <is>
+          <t>String / Teks Kategoris</t>
+        </is>
+      </c>
+      <c r="D16" s="34" t="n">
+        <v>35</v>
+      </c>
+      <c r="E16" s="34" t="n">
+        <v>35</v>
+      </c>
+      <c r="F16" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="34" t="n">
+        <v>35</v>
+      </c>
+      <c r="I16" s="33" t="inlineStr">
+        <is>
+          <t>317102******4716</t>
+        </is>
+      </c>
+      <c r="J16" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" s="36" t="inlineStr">
+        <is>
+          <t>Kardinalitas: 35 ragam nilai</t>
+        </is>
+      </c>
+      <c r="L16" s="39" t="inlineStr">
+        <is>
+          <t>Dimaskir Dinamis (Aman)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" s="28" t="inlineStr">
+        <is>
+          <t>phone_masked</t>
+        </is>
+      </c>
+      <c r="C17" s="28" t="inlineStr">
+        <is>
+          <t>String / Teks Kategoris</t>
+        </is>
+      </c>
+      <c r="D17" s="29" t="n">
+        <v>35</v>
+      </c>
+      <c r="E17" s="29" t="n">
+        <v>35</v>
+      </c>
+      <c r="F17" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="29" t="n">
+        <v>34</v>
+      </c>
+      <c r="I17" s="28" t="inlineStr">
+        <is>
+          <t>0812****381</t>
+        </is>
+      </c>
+      <c r="J17" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" s="31" t="inlineStr">
+        <is>
+          <t>Kardinalitas: 34 ragam nilai</t>
+        </is>
+      </c>
+      <c r="L17" s="38" t="inlineStr">
+        <is>
+          <t>Dimaskir Dinamis (Aman)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="32" t="n">
+        <v>10</v>
+      </c>
+      <c r="B18" s="33" t="inlineStr">
+        <is>
+          <t>customer_segment</t>
+        </is>
+      </c>
+      <c r="C18" s="33" t="inlineStr">
+        <is>
+          <t>String / Teks Kategoris</t>
+        </is>
+      </c>
+      <c r="D18" s="34" t="n">
+        <v>35</v>
+      </c>
+      <c r="E18" s="34" t="n">
+        <v>35</v>
+      </c>
+      <c r="F18" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="35" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="34" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="33" t="inlineStr">
+        <is>
+          <t>PRIORITAS</t>
+        </is>
+      </c>
+      <c r="J18" s="34" t="n">
+        <v>35</v>
+      </c>
+      <c r="K18" s="36" t="inlineStr">
+        <is>
+          <t>Kardinalitas: 1 ragam nilai</t>
+        </is>
+      </c>
+      <c r="L18" s="37" t="inlineStr">
+        <is>
+          <t>Sensitif (Perlu Proteksi)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="B19" s="28" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="inlineStr">
+        <is>
+          <t>String / Teks Kategoris</t>
+        </is>
+      </c>
+      <c r="D19" s="29" t="n">
+        <v>35</v>
+      </c>
+      <c r="E19" s="29" t="n">
+        <v>35</v>
+      </c>
+      <c r="F19" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="I19" s="28" t="inlineStr">
+        <is>
+          <t>Jakarta Selatan</t>
+        </is>
+      </c>
+      <c r="J19" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="K19" s="31" t="inlineStr">
+        <is>
+          <t>Kardinalitas: 7 ragam nilai</t>
+        </is>
+      </c>
+      <c r="L19" s="27" t="inlineStr">
+        <is>
+          <t>Data Transaksional Standar</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="B4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>